--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99194</v>
+        <v>99196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99196</v>
+        <v>99213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99213</v>
+        <v>99214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99214</v>
+        <v>99215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99215</v>
+        <v>99216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99216</v>
+        <v>99222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99222</v>
+        <v>99223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99223</v>
+        <v>99234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99234</v>
+        <v>99247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31097-2026 artfynd.xlsx
+++ b/artfynd/A 31097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856160</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135856159</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
